--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1233"/>
+  <dimension ref="A1:B1234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15224,6 +15224,18 @@
         </is>
       </c>
     </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>C61</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>CY潮穎</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1234"/>
+  <dimension ref="A1:B1235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15236,6 +15236,18 @@
         </is>
       </c>
     </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>多彩.簡元素</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1235"/>
+  <dimension ref="A1:B1236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15248,6 +15248,18 @@
         </is>
       </c>
     </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>C63</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>米米+</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1236"/>
+  <dimension ref="A1:B1237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15260,6 +15260,18 @@
         </is>
       </c>
     </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>C64</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>佰麗美</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1237"/>
+  <dimension ref="A1:B1238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15272,6 +15272,18 @@
         </is>
       </c>
     </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1238"/>
+  <dimension ref="A1:B1239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15284,6 +15284,18 @@
         </is>
       </c>
     </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1239"/>
+  <dimension ref="A1:B1240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15296,6 +15296,18 @@
         </is>
       </c>
     </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>C65</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>依美樂</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1240"/>
+  <dimension ref="A1:B1241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15308,6 +15308,18 @@
         </is>
       </c>
     </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>C66</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>依娜</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1241"/>
+  <dimension ref="A1:B1242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15320,6 +15320,18 @@
         </is>
       </c>
     </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>C67</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>藝熙</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1242"/>
+  <dimension ref="A1:B1243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15332,6 +15332,18 @@
         </is>
       </c>
     </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>C68</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>曦曦家</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1243"/>
+  <dimension ref="A1:B1244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15344,6 +15344,18 @@
         </is>
       </c>
     </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>C69</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>D‧J董靜</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1244"/>
+  <dimension ref="A1:B1245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15356,6 +15356,18 @@
         </is>
       </c>
     </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>C70</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>一帆真真</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1245"/>
+  <dimension ref="A1:B1246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15368,6 +15368,18 @@
         </is>
       </c>
     </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>C71</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>簡依</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1246"/>
+  <dimension ref="A1:B1247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15380,6 +15380,18 @@
         </is>
       </c>
     </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>C72</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>晴晴依家</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1247"/>
+  <dimension ref="A1:B1248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15392,6 +15392,18 @@
         </is>
       </c>
     </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>簡單</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1248"/>
+  <dimension ref="A1:B1249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15404,6 +15404,18 @@
         </is>
       </c>
     </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>C77</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>堯堯服飾</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1249"/>
+  <dimension ref="A1:B1250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15416,6 +15416,18 @@
         </is>
       </c>
     </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>C78</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>簡易</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
